--- a/output/pdf_financials_xlsx/NRC.xlsx
+++ b/output/pdf_financials_xlsx/NRC.xlsx
@@ -3004,19 +3004,19 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.08991</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.08991</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.08991</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.145974</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.805337</v>
       </c>
     </row>
     <row r="93">
@@ -4840,7 +4840,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -6548,7 +6552,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -6882,7 +6890,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -7168,7 +7180,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NRC.xlsx
+++ b/output/pdf_financials_xlsx/NRC.xlsx
@@ -745,7 +745,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.020854</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>-0.246187</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.285275</v>
+        <v>-1.306129</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>-0.246187</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.285275</v>
+        <v>-1.306129</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.890606</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.048736</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>4.71325</v>
@@ -1446,10 +1446,10 @@
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.890606</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.048736</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>4.71325</v>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">

--- a/output/pdf_financials_xlsx/NRC.xlsx
+++ b/output/pdf_financials_xlsx/NRC.xlsx
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.008012</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0</v>
@@ -8864,7 +8864,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
